--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProFailureInfo.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProFailureInfo.xlsx
@@ -2,54 +2,72 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24180" windowHeight="13070"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19820" windowHeight="7860"/>
   </bookViews>
   <sheets>
-    <sheet name="产品要素调整信息" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>数据状态</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <r>
+      <t>产品登记编码</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
   </si>
   <si>
-    <t>产品登记编码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>不成立原因</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
   </si>
   <si>
     <t>报告发布日期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新时间</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新人</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>不成立原因</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -58,66 +76,42 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -128,25 +122,22 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -159,7 +150,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -201,7 +192,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -236,7 +227,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -445,37 +436,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.08984375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.453125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="22.26953125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.36328125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="69.6328125" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProFailureInfo.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProFailureInfo.xlsx
@@ -122,7 +122,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -131,6 +131,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -441,7 +444,8 @@
   <cols>
     <col min="1" max="1" width="31.36328125" style="1" customWidth="1"/>
     <col min="2" max="2" width="69.6328125" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="1"/>
+    <col min="3" max="3" width="9" style="3"/>
+    <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -451,7 +455,7 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProFailureInfo.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProFailureInfo.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <r>
       <t>产品登记编码</t>
@@ -31,6 +31,7 @@
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>*</t>
@@ -42,6 +43,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -52,6 +54,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -62,12 +65,24 @@
     <t>报告发布日期</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
+  <si>
+    <t>数据状态</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新时间</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新人</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,12 +93,14 @@
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -91,11 +108,21 @@
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -122,7 +149,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -134,6 +161,9 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -439,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.36328125" style="1" customWidth="1"/>
@@ -448,15 +478,24 @@
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProFailureInfo.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProFailureInfo.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19820" windowHeight="7860"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19815" windowHeight="7860"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <r>
       <t>产品登记编码</t>
@@ -75,6 +75,10 @@
   </si>
   <si>
     <t>更新人</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品全称</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -469,32 +473,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="31.36328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="69.6328125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="3"/>
-    <col min="4" max="16384" width="9" style="1"/>
+    <col min="1" max="2" width="31.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="69.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="3"/>
+    <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -508,7 +515,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -519,7 +526,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProFailureInfo.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProFailureInfo.xlsx
@@ -66,10 +66,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>数据状态</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>更新时间</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -79,6 +75,10 @@
   </si>
   <si>
     <t>产品全称</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据状态</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -476,33 +476,33 @@
   <dimension ref="A1:G1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="2" width="31.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="69.625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9" style="3"/>
-    <col min="5" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="31.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="69.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="3"/>
+    <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
